--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129295920</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105844</v>
+        <v>105851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>91944</v>
+        <v>91951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B9" t="n">
-        <v>105844</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R9" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B10" t="n">
-        <v>80144</v>
+        <v>105851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R10" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105844</v>
+        <v>105851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>129294674</v>
       </c>
       <c r="B14" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129295137</v>
       </c>
       <c r="B15" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129296341</v>
+        <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589967</v>
+        <v>589928</v>
       </c>
       <c r="R18" t="n">
-        <v>7043822</v>
+        <v>7043805</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129296228</v>
+        <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589928</v>
+        <v>589967</v>
       </c>
       <c r="R19" t="n">
-        <v>7043805</v>
+        <v>7043822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129295993</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129295920</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129296017</v>
       </c>
       <c r="B4" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105851</v>
+        <v>105853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>91951</v>
+        <v>91953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>105853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R9" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B10" t="n">
-        <v>105851</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R10" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1653,7 +1653,7 @@
         <v>129297136</v>
       </c>
       <c r="B12" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105851</v>
+        <v>105853</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129294674</v>
+        <v>129295137</v>
       </c>
       <c r="B14" t="n">
-        <v>91558</v>
+        <v>96924</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590093</v>
+        <v>590063</v>
       </c>
       <c r="R14" t="n">
-        <v>7043893</v>
+        <v>7043902</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129295137</v>
+        <v>129294674</v>
       </c>
       <c r="B15" t="n">
-        <v>96922</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590063</v>
+        <v>590093</v>
       </c>
       <c r="R15" t="n">
-        <v>7043902</v>
+        <v>7043893</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129296228</v>
+        <v>129296341</v>
       </c>
       <c r="B18" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589928</v>
+        <v>589967</v>
       </c>
       <c r="R18" t="n">
-        <v>7043805</v>
+        <v>7043822</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129296341</v>
+        <v>129296228</v>
       </c>
       <c r="B19" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589967</v>
+        <v>589928</v>
       </c>
       <c r="R19" t="n">
-        <v>7043822</v>
+        <v>7043805</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B9" t="n">
-        <v>105853</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R9" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>105853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R10" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129295137</v>
+        <v>129294674</v>
       </c>
       <c r="B14" t="n">
-        <v>96924</v>
+        <v>91560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590063</v>
+        <v>590093</v>
       </c>
       <c r="R14" t="n">
-        <v>7043902</v>
+        <v>7043893</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129294674</v>
+        <v>129295137</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>96924</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590093</v>
+        <v>590063</v>
       </c>
       <c r="R15" t="n">
-        <v>7043893</v>
+        <v>7043902</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129294742</v>
+        <v>129296750</v>
       </c>
       <c r="B16" t="n">
-        <v>91827</v>
+        <v>91560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590090</v>
+        <v>590074</v>
       </c>
       <c r="R16" t="n">
-        <v>7043882</v>
+        <v>7043979</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129296750</v>
+        <v>129294742</v>
       </c>
       <c r="B17" t="n">
-        <v>91560</v>
+        <v>91827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590074</v>
+        <v>590090</v>
       </c>
       <c r="R17" t="n">
-        <v>7043979</v>
+        <v>7043882</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295993</v>
+        <v>129295920</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589921</v>
+        <v>589923</v>
       </c>
       <c r="R2" t="n">
-        <v>7043756</v>
+        <v>7043796</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295920</v>
+        <v>129295993</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589923</v>
+        <v>589921</v>
       </c>
       <c r="R3" t="n">
-        <v>7043796</v>
+        <v>7043756</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129294674</v>
+        <v>129295137</v>
       </c>
       <c r="B14" t="n">
-        <v>91560</v>
+        <v>96924</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590093</v>
+        <v>590063</v>
       </c>
       <c r="R14" t="n">
-        <v>7043893</v>
+        <v>7043902</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129295137</v>
+        <v>129294674</v>
       </c>
       <c r="B15" t="n">
-        <v>96924</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590063</v>
+        <v>590093</v>
       </c>
       <c r="R15" t="n">
-        <v>7043902</v>
+        <v>7043893</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129295920</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105853</v>
+        <v>105879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>91953</v>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>105879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R9" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B10" t="n">
-        <v>105853</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R10" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105853</v>
+        <v>105879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>129295137</v>
       </c>
       <c r="B14" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129294674</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129296750</v>
+        <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91560</v>
+        <v>91837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590074</v>
+        <v>590090</v>
       </c>
       <c r="R16" t="n">
-        <v>7043979</v>
+        <v>7043882</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129294742</v>
+        <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91827</v>
+        <v>91558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590090</v>
+        <v>590074</v>
       </c>
       <c r="R17" t="n">
-        <v>7043882</v>
+        <v>7043979</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129296341</v>
+        <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589967</v>
+        <v>589928</v>
       </c>
       <c r="R18" t="n">
-        <v>7043822</v>
+        <v>7043805</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129296228</v>
+        <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589928</v>
+        <v>589967</v>
       </c>
       <c r="R19" t="n">
-        <v>7043805</v>
+        <v>7043822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295920</v>
+        <v>129295993</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589923</v>
+        <v>589921</v>
       </c>
       <c r="R2" t="n">
-        <v>7043796</v>
+        <v>7043756</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295993</v>
+        <v>129295920</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589921</v>
+        <v>589923</v>
       </c>
       <c r="R3" t="n">
-        <v>7043756</v>
+        <v>7043796</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105879</v>
+        <v>105881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>105879</v>
+        <v>105881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105879</v>
+        <v>105881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>129295137</v>
       </c>
       <c r="B14" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129294674</v>
       </c>
       <c r="B15" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1961,14 +1961,10 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2041,7 +2037,7 @@
         <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2134,7 @@
         <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2155,14 +2151,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2235,7 +2227,7 @@
         <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2324,7 @@
         <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2421,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295993</v>
+        <v>129295920</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589921</v>
+        <v>589923</v>
       </c>
       <c r="R2" t="n">
-        <v>7043756</v>
+        <v>7043796</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295920</v>
+        <v>129295993</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589923</v>
+        <v>589921</v>
       </c>
       <c r="R3" t="n">
-        <v>7043796</v>
+        <v>7043756</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105881</v>
+        <v>105882</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B9" t="n">
-        <v>105881</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R9" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>105882</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R10" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105881</v>
+        <v>105882</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129295137</v>
+        <v>129294674</v>
       </c>
       <c r="B14" t="n">
-        <v>96951</v>
+        <v>91560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,23 +1855,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1879,13 +1875,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590063</v>
+        <v>590093</v>
       </c>
       <c r="R14" t="n">
-        <v>7043902</v>
+        <v>7043893</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1941,10 +1937,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129294674</v>
+        <v>129295137</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>96952</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,19 +1948,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590093</v>
+        <v>590063</v>
       </c>
       <c r="R15" t="n">
-        <v>7043893</v>
+        <v>7043902</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129294742</v>
+        <v>129296750</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>91560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,23 +2045,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2069,10 +2065,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590090</v>
+        <v>590074</v>
       </c>
       <c r="R16" t="n">
-        <v>7043882</v>
+        <v>7043979</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2131,10 +2127,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129296750</v>
+        <v>129294742</v>
       </c>
       <c r="B17" t="n">
-        <v>91560</v>
+        <v>91838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,19 +2138,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590074</v>
+        <v>590090</v>
       </c>
       <c r="R17" t="n">
-        <v>7043979</v>
+        <v>7043882</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2227,7 +2227,7 @@
         <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295920</v>
+        <v>129295993</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589923</v>
+        <v>589921</v>
       </c>
       <c r="R2" t="n">
-        <v>7043796</v>
+        <v>7043756</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295993</v>
+        <v>129295920</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589921</v>
+        <v>589923</v>
       </c>
       <c r="R3" t="n">
-        <v>7043756</v>
+        <v>7043796</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129296017</v>
       </c>
       <c r="B4" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105882</v>
+        <v>105886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>105886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R9" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B10" t="n">
-        <v>105882</v>
+        <v>80148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R10" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1653,7 +1653,7 @@
         <v>129297136</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105882</v>
+        <v>105886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129294674</v>
+        <v>129295137</v>
       </c>
       <c r="B14" t="n">
-        <v>91560</v>
+        <v>96956</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,19 +1855,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1875,13 +1879,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590093</v>
+        <v>590063</v>
       </c>
       <c r="R14" t="n">
-        <v>7043893</v>
+        <v>7043902</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1937,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129295137</v>
+        <v>129294674</v>
       </c>
       <c r="B15" t="n">
-        <v>96952</v>
+        <v>91563</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,23 +1952,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590063</v>
+        <v>590093</v>
       </c>
       <c r="R15" t="n">
-        <v>7043902</v>
+        <v>7043893</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129296750</v>
+        <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91560</v>
+        <v>91841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,19 +2045,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2065,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590074</v>
+        <v>590090</v>
       </c>
       <c r="R16" t="n">
-        <v>7043979</v>
+        <v>7043882</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2127,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129294742</v>
+        <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
+        <v>91563</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2138,23 +2142,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590090</v>
+        <v>590074</v>
       </c>
       <c r="R17" t="n">
-        <v>7043882</v>
+        <v>7043979</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2227,7 +2227,7 @@
         <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129295993</v>
       </c>
       <c r="B2" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129295920</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129296017</v>
       </c>
       <c r="B4" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105886</v>
+        <v>105888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>91966</v>
+        <v>91968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>105886</v>
+        <v>105888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129297025</v>
       </c>
       <c r="B10" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>129297136</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105886</v>
+        <v>105888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129295137</v>
+        <v>129294674</v>
       </c>
       <c r="B14" t="n">
-        <v>96956</v>
+        <v>91565</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,23 +1855,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1879,13 +1875,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590063</v>
+        <v>590093</v>
       </c>
       <c r="R14" t="n">
-        <v>7043902</v>
+        <v>7043893</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1941,10 +1937,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129294674</v>
+        <v>129295137</v>
       </c>
       <c r="B15" t="n">
-        <v>91563</v>
+        <v>96958</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,19 +1948,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590093</v>
+        <v>590063</v>
       </c>
       <c r="R15" t="n">
-        <v>7043893</v>
+        <v>7043902</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295993</v>
+        <v>129295920</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589921</v>
+        <v>589923</v>
       </c>
       <c r="R2" t="n">
-        <v>7043756</v>
+        <v>7043796</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295920</v>
+        <v>129295993</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589923</v>
+        <v>589921</v>
       </c>
       <c r="R3" t="n">
-        <v>7043796</v>
+        <v>7043756</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105888</v>
+        <v>105892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>91968</v>
+        <v>91972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>105888</v>
+        <v>105892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105888</v>
+        <v>105892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129294674</v>
+        <v>129295137</v>
       </c>
       <c r="B14" t="n">
-        <v>91565</v>
+        <v>96962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,19 +1855,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1875,13 +1879,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590093</v>
+        <v>590063</v>
       </c>
       <c r="R14" t="n">
-        <v>7043893</v>
+        <v>7043902</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1937,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129295137</v>
+        <v>129294674</v>
       </c>
       <c r="B15" t="n">
-        <v>96958</v>
+        <v>91569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,23 +1952,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590063</v>
+        <v>590093</v>
       </c>
       <c r="R15" t="n">
-        <v>7043902</v>
+        <v>7043893</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129295920</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105892</v>
+        <v>105902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>91972</v>
+        <v>91973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B9" t="n">
-        <v>105892</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R9" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>105902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R10" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105892</v>
+        <v>105902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>129295137</v>
       </c>
       <c r="B14" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129294674</v>
       </c>
       <c r="B15" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>105902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R9" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B10" t="n">
-        <v>105902</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R10" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295920</v>
+        <v>129295993</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589923</v>
+        <v>589921</v>
       </c>
       <c r="R2" t="n">
-        <v>7043796</v>
+        <v>7043756</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295993</v>
+        <v>129295920</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589921</v>
+        <v>589923</v>
       </c>
       <c r="R3" t="n">
-        <v>7043756</v>
+        <v>7043796</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129295920</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105902</v>
+        <v>105905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>91973</v>
+        <v>91976</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B9" t="n">
-        <v>105902</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R9" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>105905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R10" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105902</v>
+        <v>105905</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>129295137</v>
       </c>
       <c r="B14" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129294674</v>
       </c>
       <c r="B15" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>105905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R9" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B10" t="n">
-        <v>105905</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R10" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129294742</v>
+        <v>129296750</v>
       </c>
       <c r="B16" t="n">
-        <v>91851</v>
+        <v>91573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,23 +2045,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2069,10 +2065,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590090</v>
+        <v>590074</v>
       </c>
       <c r="R16" t="n">
-        <v>7043882</v>
+        <v>7043979</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2131,10 +2127,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129296750</v>
+        <v>129294742</v>
       </c>
       <c r="B17" t="n">
-        <v>91573</v>
+        <v>91851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,19 +2138,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590074</v>
+        <v>590090</v>
       </c>
       <c r="R17" t="n">
-        <v>7043979</v>
+        <v>7043882</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B9" t="n">
-        <v>105905</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R9" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>105905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R10" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129296750</v>
+        <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91573</v>
+        <v>91851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,19 +2045,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2065,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590074</v>
+        <v>590090</v>
       </c>
       <c r="R16" t="n">
-        <v>7043979</v>
+        <v>7043882</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2127,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129294742</v>
+        <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91851</v>
+        <v>91573</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2138,23 +2142,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590090</v>
+        <v>590074</v>
       </c>
       <c r="R17" t="n">
-        <v>7043882</v>
+        <v>7043979</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>105905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R9" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B10" t="n">
-        <v>105905</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R10" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295993</v>
+        <v>129295920</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589921</v>
+        <v>589923</v>
       </c>
       <c r="R2" t="n">
-        <v>7043756</v>
+        <v>7043796</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295920</v>
+        <v>129295993</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589923</v>
+        <v>589921</v>
       </c>
       <c r="R3" t="n">
-        <v>7043796</v>
+        <v>7043756</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B9" t="n">
-        <v>105905</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R9" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>105905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R10" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129294742</v>
+        <v>129296750</v>
       </c>
       <c r="B16" t="n">
-        <v>91851</v>
+        <v>91573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,23 +2045,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2069,10 +2065,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590090</v>
+        <v>590074</v>
       </c>
       <c r="R16" t="n">
-        <v>7043882</v>
+        <v>7043979</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2131,10 +2127,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129296750</v>
+        <v>129294742</v>
       </c>
       <c r="B17" t="n">
-        <v>91573</v>
+        <v>91851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,19 +2138,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590074</v>
+        <v>590090</v>
       </c>
       <c r="R17" t="n">
-        <v>7043979</v>
+        <v>7043882</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295920</v>
+        <v>129295993</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589923</v>
+        <v>589921</v>
       </c>
       <c r="R2" t="n">
-        <v>7043796</v>
+        <v>7043756</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295993</v>
+        <v>129295920</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589921</v>
+        <v>589923</v>
       </c>
       <c r="R3" t="n">
-        <v>7043756</v>
+        <v>7043796</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>105905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R9" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B10" t="n">
-        <v>105905</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R10" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129296750</v>
+        <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91573</v>
+        <v>91851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,19 +2045,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2065,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590074</v>
+        <v>590090</v>
       </c>
       <c r="R16" t="n">
-        <v>7043979</v>
+        <v>7043882</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2127,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129294742</v>
+        <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91851</v>
+        <v>91573</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2138,23 +2142,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590090</v>
+        <v>590074</v>
       </c>
       <c r="R17" t="n">
-        <v>7043882</v>
+        <v>7043979</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295993</v>
+        <v>129295920</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589921</v>
+        <v>589923</v>
       </c>
       <c r="R2" t="n">
-        <v>7043756</v>
+        <v>7043796</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295920</v>
+        <v>129295993</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589923</v>
+        <v>589921</v>
       </c>
       <c r="R3" t="n">
-        <v>7043796</v>
+        <v>7043756</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129296017</v>
       </c>
       <c r="B4" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105905</v>
+        <v>105934</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>91976</v>
+        <v>92004</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B9" t="n">
-        <v>105905</v>
+        <v>80175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R9" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>105934</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R10" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1653,7 +1653,7 @@
         <v>129297136</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105905</v>
+        <v>105934</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>129295137</v>
       </c>
       <c r="B14" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129294674</v>
       </c>
       <c r="B15" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295920</v>
+        <v>129295993</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>80180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589923</v>
+        <v>589921</v>
       </c>
       <c r="R2" t="n">
-        <v>7043796</v>
+        <v>7043756</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295993</v>
+        <v>129295920</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589921</v>
+        <v>589923</v>
       </c>
       <c r="R3" t="n">
-        <v>7043756</v>
+        <v>7043796</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129296017</v>
       </c>
       <c r="B4" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105934</v>
+        <v>105946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>92004</v>
+        <v>92010</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297025</v>
+        <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>80175</v>
+        <v>105946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590090</v>
+        <v>590070</v>
       </c>
       <c r="R9" t="n">
-        <v>7044059</v>
+        <v>7043906</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129295117</v>
+        <v>129297025</v>
       </c>
       <c r="B10" t="n">
-        <v>105934</v>
+        <v>80180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>674</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590070</v>
+        <v>590090</v>
       </c>
       <c r="R10" t="n">
-        <v>7043906</v>
+        <v>7044059</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1653,7 +1653,7 @@
         <v>129297136</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105934</v>
+        <v>105946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>129295137</v>
       </c>
       <c r="B14" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129294674</v>
       </c>
       <c r="B15" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295993</v>
+        <v>129295920</v>
       </c>
       <c r="B2" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589921</v>
+        <v>589923</v>
       </c>
       <c r="R2" t="n">
-        <v>7043756</v>
+        <v>7043796</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295920</v>
+        <v>129295993</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589923</v>
+        <v>589921</v>
       </c>
       <c r="R3" t="n">
-        <v>7043796</v>
+        <v>7043756</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129296017</v>
       </c>
       <c r="B4" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129296395</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129295822</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129295065</v>
       </c>
       <c r="B7" t="n">
-        <v>105946</v>
+        <v>105947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>92010</v>
+        <v>92011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129295117</v>
       </c>
       <c r="B9" t="n">
-        <v>105946</v>
+        <v>105947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129297025</v>
       </c>
       <c r="B10" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>129297136</v>
       </c>
       <c r="B12" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>105946</v>
+        <v>105947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>129295137</v>
       </c>
       <c r="B14" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129294674</v>
       </c>
       <c r="B15" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129294742</v>
       </c>
       <c r="B16" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>129296750</v>
       </c>
       <c r="B17" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>129295846</v>
       </c>
       <c r="B20" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129295920</v>
+        <v>129295137</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589923</v>
+        <v>590063</v>
       </c>
       <c r="R2" t="n">
-        <v>7043796</v>
+        <v>7043902</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129295993</v>
+        <v>129294742</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589921</v>
+        <v>590090</v>
       </c>
       <c r="R3" t="n">
-        <v>7043756</v>
+        <v>7043882</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129296017</v>
+        <v>129295065</v>
       </c>
       <c r="B4" t="n">
-        <v>80085</v>
+        <v>106356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589909</v>
+        <v>590075</v>
       </c>
       <c r="R4" t="n">
-        <v>7043766</v>
+        <v>7043898</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129296395</v>
+        <v>129295079</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>106356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589988</v>
+        <v>590069</v>
       </c>
       <c r="R5" t="n">
-        <v>7043823</v>
+        <v>7043881</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129295822</v>
+        <v>129295117</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>106356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589958</v>
+        <v>590070</v>
       </c>
       <c r="R6" t="n">
-        <v>7043777</v>
+        <v>7043906</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1134,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129295065</v>
+        <v>129297218</v>
       </c>
       <c r="B7" t="n">
-        <v>105947</v>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>674</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590075</v>
+        <v>590131</v>
       </c>
       <c r="R7" t="n">
-        <v>7043898</v>
+        <v>7043983</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1265,7 +1260,7 @@
         <v>129296060</v>
       </c>
       <c r="B8" t="n">
-        <v>92011</v>
+        <v>92333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129295117</v>
+        <v>129296017</v>
       </c>
       <c r="B9" t="n">
-        <v>105947</v>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>674</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,13 +1394,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590070</v>
+        <v>589909</v>
       </c>
       <c r="R9" t="n">
-        <v>7043906</v>
+        <v>7043766</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1461,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297025</v>
+        <v>129295993</v>
       </c>
       <c r="B10" t="n">
-        <v>80181</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,13 +1491,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590090</v>
+        <v>589921</v>
       </c>
       <c r="R10" t="n">
-        <v>7044059</v>
+        <v>7043756</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1558,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129295440</v>
+        <v>129297025</v>
       </c>
       <c r="B11" t="n">
-        <v>10964</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,16 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101449</v>
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590053</v>
+        <v>590090</v>
       </c>
       <c r="R11" t="n">
-        <v>7043912</v>
+        <v>7044059</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1653,7 +1653,7 @@
         <v>129297136</v>
       </c>
       <c r="B12" t="n">
-        <v>80181</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129295079</v>
+        <v>129295440</v>
       </c>
       <c r="B13" t="n">
-        <v>105947</v>
+        <v>10970</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>674</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Myskmåra</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590069</v>
+        <v>590053</v>
       </c>
       <c r="R13" t="n">
-        <v>7043881</v>
+        <v>7043912</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1844,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129295137</v>
+        <v>129296107</v>
       </c>
       <c r="B14" t="n">
-        <v>97015</v>
+        <v>10970</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1850,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,13 +1869,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590063</v>
+        <v>589881</v>
       </c>
       <c r="R14" t="n">
-        <v>7043902</v>
+        <v>7043804</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1941,30 +1931,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129294674</v>
+        <v>129295822</v>
       </c>
       <c r="B15" t="n">
-        <v>91608</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1972,10 +1966,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590093</v>
+        <v>589958</v>
       </c>
       <c r="R15" t="n">
-        <v>7043893</v>
+        <v>7043777</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2008,6 +2002,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2034,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129294742</v>
+        <v>129295846</v>
       </c>
       <c r="B16" t="n">
-        <v>91886</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2069,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590090</v>
+        <v>589946</v>
       </c>
       <c r="R16" t="n">
-        <v>7043882</v>
+        <v>7043792</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2105,6 +2104,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2131,30 +2135,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129296750</v>
+        <v>129295920</v>
       </c>
       <c r="B17" t="n">
-        <v>91608</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2162,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590074</v>
+        <v>589923</v>
       </c>
       <c r="R17" t="n">
-        <v>7043979</v>
+        <v>7043796</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2227,7 +2235,7 @@
         <v>129296228</v>
       </c>
       <c r="B18" t="n">
-        <v>98769</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,7 +2332,7 @@
         <v>129296341</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2418,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129295846</v>
+        <v>129296395</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2453,13 +2461,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589946</v>
+        <v>589988</v>
       </c>
       <c r="R20" t="n">
-        <v>7043792</v>
+        <v>7043823</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2489,11 +2497,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2517,6 +2520,297 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129295634</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>590023</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7043880</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129296593</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>590038</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7043930</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129295641</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>590028</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7043891</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295137</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294742</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295065</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295079</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295117</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297218</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296060</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296017</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295993</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297136</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295440</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1928,6 +1993,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296107</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295822</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295846</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295920</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296228</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296341</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296395</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295634</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296593</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,8 +2921,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295641</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>